--- a/Gap_Analysis/results/reports/comprehensive_gap_analysis.xlsx
+++ b/Gap_Analysis/results/reports/comprehensive_gap_analysis.xlsx
@@ -1544,12 +1544,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Components</t>
+          <t>Accessories</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Chains</t>
+          <t>Panniers</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1638,12 +1638,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Accessories</t>
+          <t>Components</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Panniers</t>
+          <t>Chains</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1826,12 +1826,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Components</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tights</t>
+          <t>Bottom Brackets</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bib-Shorts</t>
+          <t>Tights</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Headsets</t>
+          <t>Cranksets</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2014,12 +2014,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Components</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Forks</t>
+          <t>Bib-Shorts</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cranksets</t>
+          <t>Forks</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bottom Brackets</t>
+          <t>Headsets</t>
         </is>
       </c>
       <c r="C31" t="n">
